--- a/output/pdf_financials_xlsx/BPC.xlsx
+++ b/output/pdf_financials_xlsx/BPC.xlsx
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.01586</v>
       </c>
     </row>
     <row r="92">
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.981058</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.137944</v>
       </c>
     </row>
     <row r="93">
@@ -2520,7 +2520,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.981058</v>
       </c>
@@ -2544,7 +2548,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BPC.xlsx
+++ b/output/pdf_financials_xlsx/BPC.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008773</v>
       </c>
     </row>
     <row r="13">
@@ -785,7 +785,7 @@
         <v>-1.031092</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.526648</v>
+        <v>-4.535421</v>
       </c>
     </row>
     <row r="28">
@@ -811,7 +811,7 @@
         <v>-1.02759</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.435531</v>
+        <v>-4.444304</v>
       </c>
     </row>
     <row r="30">
@@ -824,7 +824,7 @@
         <v>-8421.488280609736</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-8921.019710378117</v>
+        <v>-8938.664521319388</v>
       </c>
     </row>
     <row r="31">
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.140093</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.960008</v>
       </c>
     </row>
     <row r="35">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.140093</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.960008</v>
       </c>
     </row>
     <row r="37">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">

--- a/output/pdf_financials_xlsx/BPC.xlsx
+++ b/output/pdf_financials_xlsx/BPC.xlsx
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.127688</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.049514</v>
       </c>
     </row>
     <row r="68">
